--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017023</v>
+        <v>125017058</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514093</v>
+        <v>514174</v>
       </c>
       <c r="R2" t="n">
-        <v>6741593</v>
+        <v>6741710</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017066</v>
+        <v>125017020</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514083</v>
+        <v>514093</v>
       </c>
       <c r="R3" t="n">
-        <v>6741605</v>
+        <v>6741595</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017058</v>
+        <v>125017039</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514174</v>
+        <v>514145</v>
       </c>
       <c r="R4" t="n">
-        <v>6741710</v>
+        <v>6741671</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017020</v>
+        <v>125017067</v>
       </c>
       <c r="B5" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514093</v>
+        <v>514091</v>
       </c>
       <c r="R5" t="n">
-        <v>6741595</v>
+        <v>6741592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017063</v>
+        <v>125017060</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514117</v>
+        <v>514141</v>
       </c>
       <c r="R7" t="n">
-        <v>6741609</v>
+        <v>6741660</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017067</v>
+        <v>125017038</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514091</v>
+        <v>514166</v>
       </c>
       <c r="R8" t="n">
-        <v>6741592</v>
+        <v>6741685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017061</v>
+        <v>125017056</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514133</v>
+        <v>514181</v>
       </c>
       <c r="R9" t="n">
-        <v>6741645</v>
+        <v>6741715</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017017</v>
+        <v>125017059</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514178</v>
+        <v>514160</v>
       </c>
       <c r="R10" t="n">
-        <v>6741721</v>
+        <v>6741676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017038</v>
+        <v>125017062</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1633,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514166</v>
+        <v>514122</v>
       </c>
       <c r="R11" t="n">
-        <v>6741685</v>
+        <v>6741638</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1679,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017060</v>
+        <v>125017023</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514141</v>
+        <v>514093</v>
       </c>
       <c r="R12" t="n">
-        <v>6741660</v>
+        <v>6741593</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017039</v>
+        <v>125017017</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514145</v>
+        <v>514178</v>
       </c>
       <c r="R13" t="n">
-        <v>6741671</v>
+        <v>6741721</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1883,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017024</v>
+        <v>125017063</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514095</v>
+        <v>514117</v>
       </c>
       <c r="R14" t="n">
-        <v>6741589</v>
+        <v>6741609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017059</v>
+        <v>125017024</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514160</v>
+        <v>514095</v>
       </c>
       <c r="R15" t="n">
-        <v>6741676</v>
+        <v>6741589</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017062</v>
+        <v>125017065</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514122</v>
+        <v>514100</v>
       </c>
       <c r="R16" t="n">
-        <v>6741638</v>
+        <v>6741610</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017065</v>
+        <v>125017061</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514100</v>
+        <v>514133</v>
       </c>
       <c r="R17" t="n">
-        <v>6741610</v>
+        <v>6741645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017056</v>
+        <v>125017066</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514181</v>
+        <v>514083</v>
       </c>
       <c r="R18" t="n">
-        <v>6741715</v>
+        <v>6741605</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017020</v>
+        <v>125017038</v>
       </c>
       <c r="B3" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514093</v>
+        <v>514166</v>
       </c>
       <c r="R3" t="n">
-        <v>6741595</v>
+        <v>6741685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017039</v>
+        <v>125017023</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514145</v>
+        <v>514093</v>
       </c>
       <c r="R4" t="n">
-        <v>6741671</v>
+        <v>6741593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017067</v>
+        <v>125017062</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514091</v>
+        <v>514122</v>
       </c>
       <c r="R5" t="n">
-        <v>6741592</v>
+        <v>6741638</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017064</v>
+        <v>125017066</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514109</v>
+        <v>514083</v>
       </c>
       <c r="R6" t="n">
-        <v>6741613</v>
+        <v>6741605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017060</v>
+        <v>125017067</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514141</v>
+        <v>514091</v>
       </c>
       <c r="R7" t="n">
-        <v>6741660</v>
+        <v>6741592</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017038</v>
+        <v>125017017</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514166</v>
+        <v>514178</v>
       </c>
       <c r="R8" t="n">
-        <v>6741685</v>
+        <v>6741721</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017056</v>
+        <v>125017024</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514181</v>
+        <v>514095</v>
       </c>
       <c r="R9" t="n">
-        <v>6741715</v>
+        <v>6741589</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017059</v>
+        <v>125017020</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514160</v>
+        <v>514093</v>
       </c>
       <c r="R10" t="n">
-        <v>6741676</v>
+        <v>6741595</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017062</v>
+        <v>125017064</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514122</v>
+        <v>514109</v>
       </c>
       <c r="R11" t="n">
-        <v>6741638</v>
+        <v>6741613</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017023</v>
+        <v>125017063</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514093</v>
+        <v>514117</v>
       </c>
       <c r="R12" t="n">
-        <v>6741593</v>
+        <v>6741609</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017017</v>
+        <v>125017065</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514178</v>
+        <v>514100</v>
       </c>
       <c r="R13" t="n">
-        <v>6741721</v>
+        <v>6741610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017063</v>
+        <v>125017061</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1949,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514117</v>
+        <v>514133</v>
       </c>
       <c r="R14" t="n">
-        <v>6741609</v>
+        <v>6741645</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017024</v>
+        <v>125017039</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514095</v>
+        <v>514145</v>
       </c>
       <c r="R15" t="n">
-        <v>6741589</v>
+        <v>6741671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017065</v>
+        <v>125017056</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514100</v>
+        <v>514181</v>
       </c>
       <c r="R16" t="n">
-        <v>6741610</v>
+        <v>6741715</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017061</v>
+        <v>125017059</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514133</v>
+        <v>514160</v>
       </c>
       <c r="R17" t="n">
-        <v>6741645</v>
+        <v>6741676</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017066</v>
+        <v>125017060</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514083</v>
+        <v>514141</v>
       </c>
       <c r="R18" t="n">
-        <v>6741605</v>
+        <v>6741660</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017058</v>
+        <v>125017065</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514174</v>
+        <v>514100</v>
       </c>
       <c r="R2" t="n">
-        <v>6741710</v>
+        <v>6741610</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017038</v>
+        <v>125017039</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514166</v>
+        <v>514145</v>
       </c>
       <c r="R3" t="n">
-        <v>6741685</v>
+        <v>6741671</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På röjd undertryckt gran</t>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017062</v>
+        <v>125017058</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514122</v>
+        <v>514174</v>
       </c>
       <c r="R5" t="n">
-        <v>6741638</v>
+        <v>6741710</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017066</v>
+        <v>125017061</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514083</v>
+        <v>514133</v>
       </c>
       <c r="R6" t="n">
-        <v>6741605</v>
+        <v>6741645</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017067</v>
+        <v>125017060</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514091</v>
+        <v>514141</v>
       </c>
       <c r="R7" t="n">
-        <v>6741592</v>
+        <v>6741660</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017017</v>
+        <v>125017038</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514178</v>
+        <v>514166</v>
       </c>
       <c r="R8" t="n">
-        <v>6741721</v>
+        <v>6741685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017024</v>
+        <v>125017066</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514095</v>
+        <v>514083</v>
       </c>
       <c r="R9" t="n">
-        <v>6741589</v>
+        <v>6741605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1598,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017064</v>
+        <v>125017017</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514109</v>
+        <v>514178</v>
       </c>
       <c r="R11" t="n">
-        <v>6741613</v>
+        <v>6741721</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017065</v>
+        <v>125017064</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514100</v>
+        <v>514109</v>
       </c>
       <c r="R13" t="n">
-        <v>6741610</v>
+        <v>6741613</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017061</v>
+        <v>125017067</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514133</v>
+        <v>514091</v>
       </c>
       <c r="R14" t="n">
-        <v>6741645</v>
+        <v>6741592</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017039</v>
+        <v>125017024</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514145</v>
+        <v>514095</v>
       </c>
       <c r="R15" t="n">
-        <v>6741671</v>
+        <v>6741589</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,11 +2087,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017056</v>
+        <v>125017062</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514181</v>
+        <v>514122</v>
       </c>
       <c r="R16" t="n">
-        <v>6741715</v>
+        <v>6741638</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017060</v>
+        <v>125017056</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514141</v>
+        <v>514181</v>
       </c>
       <c r="R18" t="n">
-        <v>6741660</v>
+        <v>6741715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017065</v>
+        <v>125017066</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514100</v>
+        <v>514083</v>
       </c>
       <c r="R2" t="n">
-        <v>6741610</v>
+        <v>6741605</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017039</v>
+        <v>125017063</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514145</v>
+        <v>514117</v>
       </c>
       <c r="R3" t="n">
-        <v>6741671</v>
+        <v>6741609</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017023</v>
+        <v>125017065</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514093</v>
+        <v>514100</v>
       </c>
       <c r="R4" t="n">
-        <v>6741593</v>
+        <v>6741610</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017058</v>
+        <v>125017062</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514174</v>
+        <v>514122</v>
       </c>
       <c r="R5" t="n">
-        <v>6741710</v>
+        <v>6741638</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017061</v>
+        <v>125017038</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514133</v>
+        <v>514166</v>
       </c>
       <c r="R6" t="n">
-        <v>6741645</v>
+        <v>6741685</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017060</v>
+        <v>125017061</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514141</v>
+        <v>514133</v>
       </c>
       <c r="R7" t="n">
-        <v>6741660</v>
+        <v>6741645</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017038</v>
+        <v>125017059</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514166</v>
+        <v>514160</v>
       </c>
       <c r="R8" t="n">
-        <v>6741685</v>
+        <v>6741676</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017066</v>
+        <v>125017056</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514083</v>
+        <v>514181</v>
       </c>
       <c r="R9" t="n">
-        <v>6741605</v>
+        <v>6741715</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017020</v>
+        <v>125017017</v>
       </c>
       <c r="B10" t="n">
-        <v>91361</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514093</v>
+        <v>514178</v>
       </c>
       <c r="R10" t="n">
-        <v>6741595</v>
+        <v>6741721</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017017</v>
+        <v>125017024</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514178</v>
+        <v>514095</v>
       </c>
       <c r="R11" t="n">
-        <v>6741721</v>
+        <v>6741589</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017063</v>
+        <v>125017064</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514117</v>
+        <v>514109</v>
       </c>
       <c r="R12" t="n">
-        <v>6741609</v>
+        <v>6741613</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017064</v>
+        <v>125017023</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514109</v>
+        <v>514093</v>
       </c>
       <c r="R13" t="n">
-        <v>6741613</v>
+        <v>6741593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017067</v>
+        <v>125017020</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514091</v>
+        <v>514093</v>
       </c>
       <c r="R14" t="n">
-        <v>6741592</v>
+        <v>6741595</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017024</v>
+        <v>125017058</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514095</v>
+        <v>514174</v>
       </c>
       <c r="R15" t="n">
-        <v>6741589</v>
+        <v>6741710</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017062</v>
+        <v>125017039</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514122</v>
+        <v>514145</v>
       </c>
       <c r="R16" t="n">
-        <v>6741638</v>
+        <v>6741671</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,6 +2184,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017059</v>
+        <v>125017060</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514160</v>
+        <v>514141</v>
       </c>
       <c r="R17" t="n">
-        <v>6741676</v>
+        <v>6741660</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017056</v>
+        <v>125017067</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514181</v>
+        <v>514091</v>
       </c>
       <c r="R18" t="n">
-        <v>6741715</v>
+        <v>6741592</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017024</v>
+        <v>125017064</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514095</v>
+        <v>514109</v>
       </c>
       <c r="R11" t="n">
-        <v>6741589</v>
+        <v>6741613</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017064</v>
+        <v>125017024</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514109</v>
+        <v>514095</v>
       </c>
       <c r="R12" t="n">
-        <v>6741613</v>
+        <v>6741589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017066</v>
+        <v>125017060</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514083</v>
+        <v>514141</v>
       </c>
       <c r="R2" t="n">
-        <v>6741605</v>
+        <v>6741660</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017063</v>
+        <v>125017062</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514117</v>
+        <v>514122</v>
       </c>
       <c r="R3" t="n">
-        <v>6741609</v>
+        <v>6741638</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017065</v>
+        <v>125017024</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514100</v>
+        <v>514095</v>
       </c>
       <c r="R4" t="n">
-        <v>6741610</v>
+        <v>6741589</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017062</v>
+        <v>125017056</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514122</v>
+        <v>514181</v>
       </c>
       <c r="R5" t="n">
-        <v>6741638</v>
+        <v>6741715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017038</v>
+        <v>125017063</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514166</v>
+        <v>514117</v>
       </c>
       <c r="R6" t="n">
-        <v>6741685</v>
+        <v>6741609</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017061</v>
+        <v>125017065</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514133</v>
+        <v>514100</v>
       </c>
       <c r="R7" t="n">
-        <v>6741645</v>
+        <v>6741610</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017059</v>
+        <v>125017061</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514160</v>
+        <v>514133</v>
       </c>
       <c r="R8" t="n">
-        <v>6741676</v>
+        <v>6741645</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017056</v>
+        <v>125017058</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514181</v>
+        <v>514174</v>
       </c>
       <c r="R9" t="n">
-        <v>6741715</v>
+        <v>6741710</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017017</v>
+        <v>125017039</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514178</v>
+        <v>514145</v>
       </c>
       <c r="R10" t="n">
-        <v>6741721</v>
+        <v>6741671</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017064</v>
+        <v>125017020</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514109</v>
+        <v>514093</v>
       </c>
       <c r="R11" t="n">
-        <v>6741613</v>
+        <v>6741595</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017024</v>
+        <v>125017066</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514095</v>
+        <v>514083</v>
       </c>
       <c r="R12" t="n">
-        <v>6741589</v>
+        <v>6741605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017023</v>
+        <v>125017059</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514093</v>
+        <v>514160</v>
       </c>
       <c r="R13" t="n">
-        <v>6741593</v>
+        <v>6741676</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017020</v>
+        <v>125017038</v>
       </c>
       <c r="B14" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514093</v>
+        <v>514166</v>
       </c>
       <c r="R14" t="n">
-        <v>6741595</v>
+        <v>6741685</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1980,6 +1980,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017058</v>
+        <v>125017067</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514174</v>
+        <v>514091</v>
       </c>
       <c r="R15" t="n">
-        <v>6741710</v>
+        <v>6741592</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017039</v>
+        <v>125017023</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514145</v>
+        <v>514093</v>
       </c>
       <c r="R16" t="n">
-        <v>6741671</v>
+        <v>6741593</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017060</v>
+        <v>125017017</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514141</v>
+        <v>514178</v>
       </c>
       <c r="R17" t="n">
-        <v>6741660</v>
+        <v>6741721</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017067</v>
+        <v>125017064</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514091</v>
+        <v>514109</v>
       </c>
       <c r="R18" t="n">
-        <v>6741592</v>
+        <v>6741613</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017060</v>
+        <v>125017067</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514141</v>
+        <v>514091</v>
       </c>
       <c r="R2" t="n">
-        <v>6741660</v>
+        <v>6741592</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017062</v>
+        <v>125017061</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514122</v>
+        <v>514133</v>
       </c>
       <c r="R3" t="n">
-        <v>6741638</v>
+        <v>6741645</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017024</v>
+        <v>125017058</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514095</v>
+        <v>514174</v>
       </c>
       <c r="R4" t="n">
-        <v>6741589</v>
+        <v>6741710</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017056</v>
+        <v>125017066</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514181</v>
+        <v>514083</v>
       </c>
       <c r="R5" t="n">
-        <v>6741715</v>
+        <v>6741605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017063</v>
+        <v>125017039</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514117</v>
+        <v>514145</v>
       </c>
       <c r="R6" t="n">
-        <v>6741609</v>
+        <v>6741671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017065</v>
+        <v>125017063</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514100</v>
+        <v>514117</v>
       </c>
       <c r="R7" t="n">
-        <v>6741610</v>
+        <v>6741609</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017061</v>
+        <v>125017064</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514133</v>
+        <v>514109</v>
       </c>
       <c r="R8" t="n">
-        <v>6741645</v>
+        <v>6741613</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017058</v>
+        <v>125017056</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514174</v>
+        <v>514181</v>
       </c>
       <c r="R9" t="n">
-        <v>6741710</v>
+        <v>6741715</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017039</v>
+        <v>125017065</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514145</v>
+        <v>514100</v>
       </c>
       <c r="R10" t="n">
-        <v>6741671</v>
+        <v>6741610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017020</v>
+        <v>125017024</v>
       </c>
       <c r="B11" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514093</v>
+        <v>514095</v>
       </c>
       <c r="R11" t="n">
-        <v>6741595</v>
+        <v>6741589</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017066</v>
+        <v>125017062</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514083</v>
+        <v>514122</v>
       </c>
       <c r="R12" t="n">
-        <v>6741605</v>
+        <v>6741638</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017059</v>
+        <v>125017038</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514160</v>
+        <v>514166</v>
       </c>
       <c r="R13" t="n">
-        <v>6741676</v>
+        <v>6741685</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017038</v>
+        <v>125017023</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514166</v>
+        <v>514093</v>
       </c>
       <c r="R14" t="n">
-        <v>6741685</v>
+        <v>6741593</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1980,11 +1985,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017067</v>
+        <v>125017017</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,25 +2023,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514091</v>
+        <v>514178</v>
       </c>
       <c r="R15" t="n">
-        <v>6741592</v>
+        <v>6741721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017023</v>
+        <v>125017020</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2125,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
         <v>514093</v>
       </c>
       <c r="R16" t="n">
-        <v>6741593</v>
+        <v>6741595</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017017</v>
+        <v>125017060</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514178</v>
+        <v>514141</v>
       </c>
       <c r="R17" t="n">
-        <v>6741721</v>
+        <v>6741660</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017064</v>
+        <v>125017059</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514109</v>
+        <v>514160</v>
       </c>
       <c r="R18" t="n">
-        <v>6741613</v>
+        <v>6741676</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017067</v>
+        <v>125017039</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514091</v>
+        <v>514145</v>
       </c>
       <c r="R2" t="n">
-        <v>6741592</v>
+        <v>6741671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017061</v>
+        <v>125017059</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514133</v>
+        <v>514160</v>
       </c>
       <c r="R3" t="n">
-        <v>6741645</v>
+        <v>6741676</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017058</v>
+        <v>125017063</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514174</v>
+        <v>514117</v>
       </c>
       <c r="R4" t="n">
-        <v>6741710</v>
+        <v>6741609</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017039</v>
+        <v>125017024</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514145</v>
+        <v>514095</v>
       </c>
       <c r="R6" t="n">
-        <v>6741671</v>
+        <v>6741589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017063</v>
+        <v>125017065</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514117</v>
+        <v>514100</v>
       </c>
       <c r="R7" t="n">
-        <v>6741609</v>
+        <v>6741610</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017064</v>
+        <v>125017060</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514109</v>
+        <v>514141</v>
       </c>
       <c r="R8" t="n">
-        <v>6741613</v>
+        <v>6741660</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017056</v>
+        <v>125017064</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514181</v>
+        <v>514109</v>
       </c>
       <c r="R9" t="n">
-        <v>6741715</v>
+        <v>6741613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017065</v>
+        <v>125017062</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514100</v>
+        <v>514122</v>
       </c>
       <c r="R10" t="n">
-        <v>6741610</v>
+        <v>6741638</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017024</v>
+        <v>125017023</v>
       </c>
       <c r="B11" t="n">
         <v>91012</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514095</v>
+        <v>514093</v>
       </c>
       <c r="R11" t="n">
-        <v>6741589</v>
+        <v>6741593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017062</v>
+        <v>125017061</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514122</v>
+        <v>514133</v>
       </c>
       <c r="R12" t="n">
-        <v>6741638</v>
+        <v>6741645</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017038</v>
+        <v>125017020</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514166</v>
+        <v>514093</v>
       </c>
       <c r="R13" t="n">
-        <v>6741685</v>
+        <v>6741595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017023</v>
+        <v>125017058</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514093</v>
+        <v>514174</v>
       </c>
       <c r="R14" t="n">
-        <v>6741593</v>
+        <v>6741710</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017020</v>
+        <v>125017056</v>
       </c>
       <c r="B16" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514093</v>
+        <v>514181</v>
       </c>
       <c r="R16" t="n">
-        <v>6741595</v>
+        <v>6741715</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017060</v>
+        <v>125017038</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514141</v>
+        <v>514166</v>
       </c>
       <c r="R17" t="n">
-        <v>6741660</v>
+        <v>6741685</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017059</v>
+        <v>125017067</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514160</v>
+        <v>514091</v>
       </c>
       <c r="R18" t="n">
-        <v>6741676</v>
+        <v>6741592</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017024</v>
+        <v>125017065</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514095</v>
+        <v>514100</v>
       </c>
       <c r="R6" t="n">
-        <v>6741589</v>
+        <v>6741610</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017065</v>
+        <v>125017024</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514100</v>
+        <v>514095</v>
       </c>
       <c r="R7" t="n">
-        <v>6741610</v>
+        <v>6741589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017058</v>
+        <v>125017017</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514174</v>
+        <v>514178</v>
       </c>
       <c r="R14" t="n">
-        <v>6741710</v>
+        <v>6741721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017017</v>
+        <v>125017058</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514178</v>
+        <v>514174</v>
       </c>
       <c r="R15" t="n">
-        <v>6741721</v>
+        <v>6741710</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017039</v>
+        <v>125017056</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514145</v>
+        <v>514181</v>
       </c>
       <c r="R2" t="n">
-        <v>6741671</v>
+        <v>6741715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017059</v>
+        <v>125017038</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514160</v>
+        <v>514166</v>
       </c>
       <c r="R3" t="n">
-        <v>6741676</v>
+        <v>6741685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017063</v>
+        <v>125017017</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514117</v>
+        <v>514178</v>
       </c>
       <c r="R4" t="n">
-        <v>6741609</v>
+        <v>6741721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017066</v>
+        <v>125017061</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514083</v>
+        <v>514133</v>
       </c>
       <c r="R5" t="n">
-        <v>6741605</v>
+        <v>6741645</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017065</v>
+        <v>125017060</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514100</v>
+        <v>514141</v>
       </c>
       <c r="R6" t="n">
-        <v>6741610</v>
+        <v>6741660</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017024</v>
+        <v>125017058</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514095</v>
+        <v>514174</v>
       </c>
       <c r="R7" t="n">
-        <v>6741589</v>
+        <v>6741710</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017060</v>
+        <v>125017066</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514141</v>
+        <v>514083</v>
       </c>
       <c r="R8" t="n">
-        <v>6741660</v>
+        <v>6741605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017064</v>
+        <v>125017023</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514109</v>
+        <v>514093</v>
       </c>
       <c r="R9" t="n">
-        <v>6741613</v>
+        <v>6741593</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017062</v>
+        <v>125017024</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514122</v>
+        <v>514095</v>
       </c>
       <c r="R10" t="n">
-        <v>6741638</v>
+        <v>6741589</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017023</v>
+        <v>125017067</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514093</v>
+        <v>514091</v>
       </c>
       <c r="R11" t="n">
-        <v>6741593</v>
+        <v>6741592</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017061</v>
+        <v>125017020</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514133</v>
+        <v>514093</v>
       </c>
       <c r="R12" t="n">
-        <v>6741645</v>
+        <v>6741595</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017020</v>
+        <v>125017062</v>
       </c>
       <c r="B13" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514093</v>
+        <v>514122</v>
       </c>
       <c r="R13" t="n">
-        <v>6741595</v>
+        <v>6741638</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017017</v>
+        <v>125017059</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514178</v>
+        <v>514160</v>
       </c>
       <c r="R14" t="n">
-        <v>6741721</v>
+        <v>6741676</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017058</v>
+        <v>125017039</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514174</v>
+        <v>514145</v>
       </c>
       <c r="R15" t="n">
-        <v>6741710</v>
+        <v>6741671</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017056</v>
+        <v>125017063</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514181</v>
+        <v>514117</v>
       </c>
       <c r="R16" t="n">
-        <v>6741715</v>
+        <v>6741609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017038</v>
+        <v>125017065</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514166</v>
+        <v>514100</v>
       </c>
       <c r="R17" t="n">
-        <v>6741685</v>
+        <v>6741610</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017067</v>
+        <v>125017064</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514091</v>
+        <v>514109</v>
       </c>
       <c r="R18" t="n">
-        <v>6741592</v>
+        <v>6741613</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017056</v>
+        <v>125017024</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514181</v>
+        <v>514095</v>
       </c>
       <c r="R2" t="n">
-        <v>6741715</v>
+        <v>6741589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017038</v>
+        <v>125017060</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514166</v>
+        <v>514141</v>
       </c>
       <c r="R3" t="n">
-        <v>6741685</v>
+        <v>6741660</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017017</v>
+        <v>125017066</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514178</v>
+        <v>514083</v>
       </c>
       <c r="R4" t="n">
-        <v>6741721</v>
+        <v>6741605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017061</v>
+        <v>125017062</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514133</v>
+        <v>514122</v>
       </c>
       <c r="R5" t="n">
-        <v>6741645</v>
+        <v>6741638</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017060</v>
+        <v>125017067</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514141</v>
+        <v>514091</v>
       </c>
       <c r="R6" t="n">
-        <v>6741660</v>
+        <v>6741592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017058</v>
+        <v>125017017</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514174</v>
+        <v>514178</v>
       </c>
       <c r="R7" t="n">
-        <v>6741710</v>
+        <v>6741721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017066</v>
+        <v>125017039</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514083</v>
+        <v>514145</v>
       </c>
       <c r="R8" t="n">
-        <v>6741605</v>
+        <v>6741671</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017023</v>
+        <v>125017058</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514093</v>
+        <v>514174</v>
       </c>
       <c r="R9" t="n">
-        <v>6741593</v>
+        <v>6741710</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017024</v>
+        <v>125017056</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514095</v>
+        <v>514181</v>
       </c>
       <c r="R10" t="n">
-        <v>6741589</v>
+        <v>6741715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017067</v>
+        <v>125017061</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514091</v>
+        <v>514133</v>
       </c>
       <c r="R11" t="n">
-        <v>6741592</v>
+        <v>6741645</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017020</v>
+        <v>125017038</v>
       </c>
       <c r="B12" t="n">
-        <v>91361</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514093</v>
+        <v>514166</v>
       </c>
       <c r="R12" t="n">
-        <v>6741595</v>
+        <v>6741685</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017062</v>
+        <v>125017023</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514122</v>
+        <v>514093</v>
       </c>
       <c r="R13" t="n">
-        <v>6741638</v>
+        <v>6741593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017059</v>
+        <v>125017020</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91361</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514160</v>
+        <v>514093</v>
       </c>
       <c r="R14" t="n">
-        <v>6741676</v>
+        <v>6741595</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017039</v>
+        <v>125017064</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514145</v>
+        <v>514109</v>
       </c>
       <c r="R15" t="n">
-        <v>6741671</v>
+        <v>6741613</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,11 +2087,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017063</v>
+        <v>125017059</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514117</v>
+        <v>514160</v>
       </c>
       <c r="R16" t="n">
-        <v>6741609</v>
+        <v>6741676</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017064</v>
+        <v>125017063</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514109</v>
+        <v>514117</v>
       </c>
       <c r="R18" t="n">
-        <v>6741613</v>
+        <v>6741609</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017024</v>
+        <v>125017066</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514095</v>
+        <v>514083</v>
       </c>
       <c r="R2" t="n">
-        <v>6741589</v>
+        <v>6741605</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017060</v>
+        <v>125017062</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514141</v>
+        <v>514122</v>
       </c>
       <c r="R3" t="n">
-        <v>6741660</v>
+        <v>6741638</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017066</v>
+        <v>125017056</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514083</v>
+        <v>514181</v>
       </c>
       <c r="R4" t="n">
-        <v>6741605</v>
+        <v>6741715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017062</v>
+        <v>125017061</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514122</v>
+        <v>514133</v>
       </c>
       <c r="R5" t="n">
-        <v>6741638</v>
+        <v>6741645</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017067</v>
+        <v>125017064</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514091</v>
+        <v>514109</v>
       </c>
       <c r="R6" t="n">
-        <v>6741592</v>
+        <v>6741613</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>125017017</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>91131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017039</v>
+        <v>125017020</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91521</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514145</v>
+        <v>514093</v>
       </c>
       <c r="R8" t="n">
-        <v>6741671</v>
+        <v>6741595</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017058</v>
+        <v>125017024</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514174</v>
+        <v>514095</v>
       </c>
       <c r="R9" t="n">
-        <v>6741710</v>
+        <v>6741589</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017056</v>
+        <v>125017059</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514181</v>
+        <v>514160</v>
       </c>
       <c r="R10" t="n">
-        <v>6741715</v>
+        <v>6741676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017061</v>
+        <v>125017038</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514133</v>
+        <v>514166</v>
       </c>
       <c r="R11" t="n">
-        <v>6741645</v>
+        <v>6741685</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017038</v>
+        <v>125017039</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514166</v>
+        <v>514145</v>
       </c>
       <c r="R12" t="n">
-        <v>6741685</v>
+        <v>6741671</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På röjd undertryckt gran</t>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017023</v>
+        <v>125017065</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514093</v>
+        <v>514100</v>
       </c>
       <c r="R13" t="n">
-        <v>6741593</v>
+        <v>6741610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017020</v>
+        <v>125017058</v>
       </c>
       <c r="B14" t="n">
-        <v>91361</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514093</v>
+        <v>514174</v>
       </c>
       <c r="R14" t="n">
-        <v>6741595</v>
+        <v>6741710</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017064</v>
+        <v>125017060</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514109</v>
+        <v>514141</v>
       </c>
       <c r="R15" t="n">
-        <v>6741613</v>
+        <v>6741660</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017059</v>
+        <v>125017067</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514160</v>
+        <v>514091</v>
       </c>
       <c r="R16" t="n">
-        <v>6741676</v>
+        <v>6741592</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017065</v>
+        <v>125017023</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514100</v>
+        <v>514093</v>
       </c>
       <c r="R17" t="n">
-        <v>6741610</v>
+        <v>6741593</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,7 +2320,7 @@
         <v>125017063</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017060</v>
+        <v>125017067</v>
       </c>
       <c r="B15" t="n">
         <v>78947</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514141</v>
+        <v>514091</v>
       </c>
       <c r="R15" t="n">
-        <v>6741660</v>
+        <v>6741592</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017067</v>
+        <v>125017060</v>
       </c>
       <c r="B16" t="n">
         <v>78947</v>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514091</v>
+        <v>514141</v>
       </c>
       <c r="R16" t="n">
-        <v>6741592</v>
+        <v>6741660</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017066</v>
+        <v>125017060</v>
       </c>
       <c r="B2" t="n">
         <v>78947</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514083</v>
+        <v>514141</v>
       </c>
       <c r="R2" t="n">
-        <v>6741605</v>
+        <v>6741660</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017062</v>
+        <v>125017059</v>
       </c>
       <c r="B3" t="n">
         <v>78947</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514122</v>
+        <v>514160</v>
       </c>
       <c r="R3" t="n">
-        <v>6741638</v>
+        <v>6741676</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017056</v>
+        <v>125017039</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514181</v>
+        <v>514145</v>
       </c>
       <c r="R4" t="n">
-        <v>6741715</v>
+        <v>6741671</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017061</v>
+        <v>125017020</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>91521</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514133</v>
+        <v>514093</v>
       </c>
       <c r="R5" t="n">
-        <v>6741645</v>
+        <v>6741595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017064</v>
+        <v>125017056</v>
       </c>
       <c r="B6" t="n">
         <v>78947</v>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514109</v>
+        <v>514181</v>
       </c>
       <c r="R6" t="n">
-        <v>6741613</v>
+        <v>6741715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017017</v>
+        <v>125017067</v>
       </c>
       <c r="B7" t="n">
-        <v>91131</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514178</v>
+        <v>514091</v>
       </c>
       <c r="R7" t="n">
-        <v>6741721</v>
+        <v>6741592</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017020</v>
+        <v>125017063</v>
       </c>
       <c r="B8" t="n">
-        <v>91521</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514093</v>
+        <v>514117</v>
       </c>
       <c r="R8" t="n">
-        <v>6741595</v>
+        <v>6741609</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017024</v>
+        <v>125017064</v>
       </c>
       <c r="B9" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514095</v>
+        <v>514109</v>
       </c>
       <c r="R9" t="n">
-        <v>6741589</v>
+        <v>6741613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017059</v>
+        <v>125017024</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514160</v>
+        <v>514095</v>
       </c>
       <c r="R10" t="n">
-        <v>6741676</v>
+        <v>6741589</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017038</v>
+        <v>125017023</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514166</v>
+        <v>514093</v>
       </c>
       <c r="R11" t="n">
-        <v>6741685</v>
+        <v>6741593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1674,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017039</v>
+        <v>125017066</v>
       </c>
       <c r="B12" t="n">
         <v>78947</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514145</v>
+        <v>514083</v>
       </c>
       <c r="R12" t="n">
-        <v>6741671</v>
+        <v>6741605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017065</v>
+        <v>125017058</v>
       </c>
       <c r="B13" t="n">
         <v>78947</v>
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514100</v>
+        <v>514174</v>
       </c>
       <c r="R13" t="n">
-        <v>6741610</v>
+        <v>6741710</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017058</v>
+        <v>125017061</v>
       </c>
       <c r="B14" t="n">
         <v>78947</v>
@@ -1949,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514174</v>
+        <v>514133</v>
       </c>
       <c r="R14" t="n">
-        <v>6741710</v>
+        <v>6741645</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017067</v>
+        <v>125017062</v>
       </c>
       <c r="B15" t="n">
         <v>78947</v>
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514091</v>
+        <v>514122</v>
       </c>
       <c r="R15" t="n">
-        <v>6741592</v>
+        <v>6741638</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017060</v>
+        <v>125017017</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>91131</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514141</v>
+        <v>514178</v>
       </c>
       <c r="R16" t="n">
-        <v>6741660</v>
+        <v>6741721</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017023</v>
+        <v>125017065</v>
       </c>
       <c r="B17" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514093</v>
+        <v>514100</v>
       </c>
       <c r="R17" t="n">
-        <v>6741593</v>
+        <v>6741610</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017063</v>
+        <v>125017038</v>
       </c>
       <c r="B18" t="n">
         <v>78947</v>
@@ -2357,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514117</v>
+        <v>514166</v>
       </c>
       <c r="R18" t="n">
-        <v>6741609</v>
+        <v>6741685</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,6 +2388,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017059</v>
+        <v>125017039</v>
       </c>
       <c r="B3" t="n">
         <v>78947</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514160</v>
+        <v>514145</v>
       </c>
       <c r="R3" t="n">
-        <v>6741676</v>
+        <v>6741671</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017039</v>
+        <v>125017059</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514145</v>
+        <v>514160</v>
       </c>
       <c r="R4" t="n">
-        <v>6741671</v>
+        <v>6741676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15377-2025 artfynd.xlsx
+++ b/artfynd/A 15377-2025 artfynd.xlsx
@@ -675,16 +675,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017060</v>
+        <v>125017065</v>
       </c>
       <c r="B2" t="n">
         <v>78947</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>NT</t>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514141</v>
+        <v>514100</v>
       </c>
       <c r="R2" t="n">
-        <v>6741660</v>
+        <v>6741610</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017039</v>
+        <v>125017023</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514145</v>
+        <v>514093</v>
       </c>
       <c r="R3" t="n">
-        <v>6741671</v>
+        <v>6741593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,16 +869,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017059</v>
+        <v>125017064</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>NT</t>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514160</v>
+        <v>514109</v>
       </c>
       <c r="R4" t="n">
-        <v>6741676</v>
+        <v>6741613</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017020</v>
+        <v>125017056</v>
       </c>
       <c r="B5" t="n">
-        <v>91521</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514093</v>
+        <v>514181</v>
       </c>
       <c r="R5" t="n">
-        <v>6741595</v>
+        <v>6741715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017056</v>
+        <v>125017024</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514181</v>
+        <v>514095</v>
       </c>
       <c r="R6" t="n">
-        <v>6741715</v>
+        <v>6741589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,11 +1165,6 @@
       <c r="B7" t="n">
         <v>78947</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1292,16 +1257,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017063</v>
+        <v>125017039</v>
       </c>
       <c r="B8" t="n">
         <v>78947</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1332,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514117</v>
+        <v>514145</v>
       </c>
       <c r="R8" t="n">
-        <v>6741609</v>
+        <v>6741671</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,16 +1359,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017064</v>
+        <v>125017059</v>
       </c>
       <c r="B9" t="n">
         <v>78947</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1434,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514109</v>
+        <v>514160</v>
       </c>
       <c r="R9" t="n">
-        <v>6741613</v>
+        <v>6741676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,15 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017024</v>
+        <v>125017060</v>
       </c>
       <c r="B10" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514095</v>
+        <v>514141</v>
       </c>
       <c r="R10" t="n">
-        <v>6741589</v>
+        <v>6741660</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,15 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017023</v>
+        <v>125017066</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514093</v>
+        <v>514083</v>
       </c>
       <c r="R11" t="n">
-        <v>6741593</v>
+        <v>6741605</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,37 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017066</v>
+        <v>125017017</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514083</v>
+        <v>514178</v>
       </c>
       <c r="R12" t="n">
-        <v>6741605</v>
+        <v>6741721</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,37 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017058</v>
+        <v>125017020</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514174</v>
+        <v>514093</v>
       </c>
       <c r="R13" t="n">
-        <v>6741710</v>
+        <v>6741595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,16 +1844,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017061</v>
+        <v>125017038</v>
       </c>
       <c r="B14" t="n">
         <v>78947</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1944,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514133</v>
+        <v>514166</v>
       </c>
       <c r="R14" t="n">
-        <v>6741645</v>
+        <v>6741685</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1980,6 +1915,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,16 +1946,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017062</v>
+        <v>125017058</v>
       </c>
       <c r="B15" t="n">
         <v>78947</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2046,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514122</v>
+        <v>514174</v>
       </c>
       <c r="R15" t="n">
-        <v>6741638</v>
+        <v>6741710</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,37 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017017</v>
+        <v>125017063</v>
       </c>
       <c r="B16" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514178</v>
+        <v>514117</v>
       </c>
       <c r="R16" t="n">
-        <v>6741721</v>
+        <v>6741609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,16 +2140,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017065</v>
+        <v>125017061</v>
       </c>
       <c r="B17" t="n">
         <v>78947</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2250,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514100</v>
+        <v>514133</v>
       </c>
       <c r="R17" t="n">
-        <v>6741610</v>
+        <v>6741645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,16 +2237,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017038</v>
+        <v>125017062</v>
       </c>
       <c r="B18" t="n">
         <v>78947</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2352,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514166</v>
+        <v>514122</v>
       </c>
       <c r="R18" t="n">
-        <v>6741685</v>
+        <v>6741638</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
